--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N99_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N99_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.81575355082168</v>
+        <v>4.520059952008523</v>
       </c>
       <c r="D2" t="n">
-        <v>27.79612739915571</v>
+        <v>4.516870702362803</v>
       </c>
       <c r="E2" t="n">
-        <v>12.276903917244</v>
+        <v>1.994996886552151</v>
       </c>
       <c r="F2" t="n">
-        <v>11.9914458984588</v>
+        <v>1.948609958499554</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.78518932289021</v>
+        <v>7.44009326496966</v>
       </c>
       <c r="D3" t="n">
-        <v>36.61613903753962</v>
+        <v>5.950122593600188</v>
       </c>
       <c r="E3" t="n">
-        <v>12.276903917244</v>
+        <v>1.994996886552151</v>
       </c>
       <c r="F3" t="n">
-        <v>11.9914458984588</v>
+        <v>1.948609958499554</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.97047961700585</v>
+        <v>3.732702937763451</v>
       </c>
       <c r="D4" t="n">
-        <v>8.062257748298549</v>
+        <v>1.310116884098514</v>
       </c>
       <c r="E4" t="n">
-        <v>12.276903917244</v>
+        <v>1.994996886552151</v>
       </c>
       <c r="F4" t="n">
-        <v>11.9914458984588</v>
+        <v>1.948609958499554</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.395435164964129</v>
+        <v>1.201758214306671</v>
       </c>
       <c r="D5" t="n">
-        <v>7.654761626536329</v>
+        <v>1.243898764312154</v>
       </c>
       <c r="E5" t="n">
-        <v>12.276903917244</v>
+        <v>1.994996886552151</v>
       </c>
       <c r="F5" t="n">
-        <v>11.9914458984588</v>
+        <v>1.948609958499554</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.88410332017245</v>
+        <v>3.881166789528024</v>
       </c>
       <c r="D6" t="n">
-        <v>9.592746935740175</v>
+        <v>1.558821377057779</v>
       </c>
       <c r="E6" t="n">
-        <v>12.276903917244</v>
+        <v>1.994996886552151</v>
       </c>
       <c r="F6" t="n">
-        <v>11.9914458984588</v>
+        <v>1.948609958499554</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
